--- a/public/tally_templates/OBWH.xlsx
+++ b/public/tally_templates/OBWH.xlsx
@@ -1124,7 +1124,7 @@
       <alignment horizontal="general" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="663">
+  <cellXfs count="669">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -3037,6 +3037,24 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="59" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="23">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="22">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="33">
@@ -3300,7 +3318,7 @@
           <t xml:space="preserve"> M/V       :  </t>
         </is>
       </c>
-      <c r="B4" s="345" t="n"/>
+      <c r="B4" s="137" t="n"/>
       <c r="C4" s="346" t="n"/>
       <c r="D4" s="344" t="n"/>
       <c r="E4" s="342" t="n"/>
@@ -3310,7 +3328,7 @@
           <t xml:space="preserve">DATE :  </t>
         </is>
       </c>
-      <c r="H4" s="346" t="n"/>
+      <c r="H4" s="663" t="n"/>
       <c r="I4" s="345" t="n"/>
     </row>
     <row r="5" ht="9.75" customHeight="1" s="340">
@@ -3330,7 +3348,7 @@
           <t xml:space="preserve">  Voy. No.  : </t>
         </is>
       </c>
-      <c r="B6" s="345" t="n"/>
+      <c r="B6" s="137" t="n"/>
       <c r="C6" s="348" t="n"/>
       <c r="D6" s="345" t="inlineStr">
         <is>
@@ -3371,14 +3389,14 @@
           <t xml:space="preserve">   Disch.  Com'ced work :</t>
         </is>
       </c>
-      <c r="E8" s="344" t="n"/>
+      <c r="E8" s="664" t="n"/>
       <c r="F8" s="345" t="n"/>
       <c r="G8" s="345" t="inlineStr">
         <is>
           <t xml:space="preserve"> Load. Com'ced work : </t>
         </is>
       </c>
-      <c r="H8" s="345" t="n"/>
+      <c r="H8" s="137" t="n"/>
       <c r="I8" s="351" t="n"/>
     </row>
     <row r="9" ht="9.9" customHeight="1" s="340">
@@ -3401,14 +3419,14 @@
           <t xml:space="preserve">                         Com'ted work :</t>
         </is>
       </c>
-      <c r="E10" s="344" t="n"/>
+      <c r="E10" s="664" t="n"/>
       <c r="F10" s="345" t="n"/>
       <c r="G10" s="345" t="inlineStr">
         <is>
           <t xml:space="preserve">           Com'ted work : </t>
         </is>
       </c>
-      <c r="H10" s="345" t="n"/>
+      <c r="H10" s="137" t="n"/>
       <c r="I10" s="352" t="n"/>
     </row>
     <row r="11" ht="5.25" customHeight="1" s="340">
@@ -4614,7 +4632,7 @@
           <t>M / V  :</t>
         </is>
       </c>
-      <c r="B6" s="345" t="n"/>
+      <c r="B6" s="137" t="n"/>
       <c r="C6" s="345" t="n"/>
       <c r="D6" s="345" t="n"/>
       <c r="E6" s="345" t="n"/>
@@ -4656,7 +4674,7 @@
           <t xml:space="preserve">PORT   :  </t>
         </is>
       </c>
-      <c r="B8" s="345" t="inlineStr">
+      <c r="B8" s="137" t="inlineStr">
         <is>
           <t>PYEONGTAEK, KOREA</t>
         </is>
@@ -4670,7 +4688,7 @@
           <t>PIER    :</t>
         </is>
       </c>
-      <c r="H8" s="352" t="inlineStr">
+      <c r="H8" s="137" t="inlineStr">
         <is>
           <t>PNCT</t>
         </is>
@@ -4681,7 +4699,7 @@
           <t xml:space="preserve">BERTH  : </t>
         </is>
       </c>
-      <c r="L8" s="352" t="n">
+      <c r="L8" s="137" t="n">
         <v>15</v>
       </c>
       <c r="M8" s="345" t="n"/>
@@ -5538,7 +5556,7 @@
           <t xml:space="preserve">M / V :  </t>
         </is>
       </c>
-      <c r="B6" s="345" t="inlineStr">
+      <c r="B6" s="137" t="inlineStr">
         <is>
           <t xml:space="preserve"> OCEAN BLUE WHALE</t>
         </is>
@@ -5554,7 +5572,7 @@
           <t xml:space="preserve">VOY. NO. :    </t>
         </is>
       </c>
-      <c r="J6" s="345" t="n"/>
+      <c r="J6" s="137" t="n"/>
       <c r="K6" s="351">
         <f>'Final work rpt-voucher'!C6</f>
         <v/>
@@ -5592,7 +5610,7 @@
           <t xml:space="preserve">PORT  : </t>
         </is>
       </c>
-      <c r="B8" s="351" t="inlineStr">
+      <c r="B8" s="137" t="inlineStr">
         <is>
           <t xml:space="preserve"> PYEONGTAEK, KOREA</t>
         </is>
@@ -5615,7 +5633,7 @@
           <t xml:space="preserve">BERTH  : </t>
         </is>
       </c>
-      <c r="P8" s="350" t="n">
+      <c r="P8" s="137" t="n">
         <v>15</v>
       </c>
       <c r="Q8" s="345" t="n"/>
@@ -5641,7 +5659,7 @@
       <c r="Q9" s="345" t="n"/>
       <c r="R9" s="345" t="n"/>
     </row>
-    <row r="10" ht="12" customHeight="1" s="340">
+    <row r="10" ht="16.2" customHeight="1" s="340">
       <c r="A10" s="485" t="inlineStr">
         <is>
           <t>PORT</t>
@@ -5689,7 +5707,7 @@
       <c r="Q10" s="479" t="n"/>
       <c r="R10" s="486" t="n"/>
     </row>
-    <row r="11" ht="12" customHeight="1" s="340">
+    <row r="11" ht="16.2" customHeight="1" s="340">
       <c r="A11" s="488" t="n"/>
       <c r="B11" s="488" t="n"/>
       <c r="C11" s="489" t="n"/>
@@ -6542,7 +6560,7 @@
           <t>M / V  :</t>
         </is>
       </c>
-      <c r="B6" s="351" t="n"/>
+      <c r="B6" s="137" t="n"/>
       <c r="C6" s="345" t="n"/>
       <c r="D6" s="345" t="n"/>
       <c r="E6" s="345" t="n"/>
@@ -6584,7 +6602,7 @@
           <t xml:space="preserve">PORT   :  </t>
         </is>
       </c>
-      <c r="B8" s="345" t="inlineStr">
+      <c r="B8" s="137" t="inlineStr">
         <is>
           <t>PYEONGTAEK, KOREA</t>
         </is>
@@ -6598,7 +6616,7 @@
           <t>PIER    :</t>
         </is>
       </c>
-      <c r="H8" s="352" t="inlineStr">
+      <c r="H8" s="137" t="inlineStr">
         <is>
           <t>PNCT</t>
         </is>
@@ -6609,7 +6627,7 @@
           <t xml:space="preserve">BERTH  : </t>
         </is>
       </c>
-      <c r="L8" s="352" t="n">
+      <c r="L8" s="137" t="n">
         <v>15</v>
       </c>
       <c r="M8" s="345" t="n"/>
@@ -7563,7 +7581,7 @@
           <t xml:space="preserve">M / V :  </t>
         </is>
       </c>
-      <c r="B6" s="351" t="inlineStr">
+      <c r="B6" s="137" t="inlineStr">
         <is>
           <t xml:space="preserve"> OCEAN BLUE WHALE</t>
         </is>
@@ -7579,7 +7597,7 @@
           <t xml:space="preserve">VOY. NO. :   </t>
         </is>
       </c>
-      <c r="J6" s="345" t="n"/>
+      <c r="J6" s="137" t="n"/>
       <c r="K6" s="482">
         <f>'Final work rpt-voucher'!E6</f>
         <v/>
@@ -7617,7 +7635,7 @@
           <t xml:space="preserve">PORT  : </t>
         </is>
       </c>
-      <c r="B8" s="351" t="inlineStr">
+      <c r="B8" s="137" t="inlineStr">
         <is>
           <t xml:space="preserve"> PYEONGTAEK, KOREA</t>
         </is>
@@ -7640,7 +7658,7 @@
           <t xml:space="preserve">BERTH  : </t>
         </is>
       </c>
-      <c r="P8" s="350" t="n">
+      <c r="P8" s="137" t="n">
         <v>15</v>
       </c>
       <c r="Q8" s="345" t="n"/>
@@ -7666,7 +7684,7 @@
       <c r="Q9" s="345" t="n"/>
       <c r="R9" s="345" t="n"/>
     </row>
-    <row r="10" ht="12" customHeight="1" s="340">
+    <row r="10" ht="16.2" customHeight="1" s="340">
       <c r="A10" s="485" t="inlineStr">
         <is>
           <t>PORT</t>
@@ -7714,7 +7732,7 @@
       <c r="Q10" s="479" t="n"/>
       <c r="R10" s="486" t="n"/>
     </row>
-    <row r="11" ht="12" customHeight="1" s="340">
+    <row r="11" ht="16.2" customHeight="1" s="340">
       <c r="A11" s="488" t="n"/>
       <c r="B11" s="488" t="n"/>
       <c r="C11" s="489" t="n"/>
@@ -8564,7 +8582,7 @@
           <t>M / V :</t>
         </is>
       </c>
-      <c r="B6" s="547" t="inlineStr">
+      <c r="B6" s="665" t="inlineStr">
         <is>
           <t>OCEAN BLUE WHALE</t>
         </is>
@@ -8608,7 +8626,7 @@
           <t xml:space="preserve">CONTAINER NO : </t>
         </is>
       </c>
-      <c r="B8" s="467" t="n"/>
+      <c r="B8" s="665" t="n"/>
       <c r="C8" s="467" t="n"/>
       <c r="D8" s="467" t="n"/>
       <c r="E8" s="467" t="n"/>
@@ -8617,18 +8635,14 @@
           <t xml:space="preserve"> SEAL NO.  : </t>
         </is>
       </c>
-      <c r="H8" s="548" t="inlineStr">
-        <is>
-          <t>FULL</t>
-        </is>
-      </c>
+      <c r="H8" s="665"/>
       <c r="I8" s="467" t="n"/>
       <c r="J8" s="467" t="inlineStr">
         <is>
           <t xml:space="preserve"> SIZE   :  </t>
         </is>
       </c>
-      <c r="K8" s="548" t="inlineStr">
+      <c r="K8" s="665" t="inlineStr">
         <is>
           <t>20'</t>
         </is>
@@ -10174,7 +10188,7 @@
           <t>Description of Damage :</t>
         </is>
       </c>
-      <c r="D29" s="561" t="n"/>
+      <c r="D29" s="666" t="n"/>
       <c r="E29" s="561" t="n"/>
       <c r="F29" s="561" t="n"/>
       <c r="G29" s="561" t="n"/>
@@ -13838,7 +13852,7 @@
           <t>M / V :</t>
         </is>
       </c>
-      <c r="B55" s="547" t="inlineStr">
+      <c r="B55" s="665" t="inlineStr">
         <is>
           <t>OCEAN BLUE WHALE</t>
         </is>
@@ -13882,7 +13896,7 @@
           <t xml:space="preserve">CONTAINER NO : </t>
         </is>
       </c>
-      <c r="B57" s="467" t="n"/>
+      <c r="B57" s="665" t="n"/>
       <c r="C57" s="467" t="n"/>
       <c r="D57" s="467" t="n"/>
       <c r="E57" s="467" t="n"/>
@@ -13891,18 +13905,14 @@
           <t xml:space="preserve"> SEAL NO.  : </t>
         </is>
       </c>
-      <c r="H57" s="548" t="inlineStr">
-        <is>
-          <t>FULL</t>
-        </is>
-      </c>
+      <c r="H57" s="665"/>
       <c r="I57" s="467" t="n"/>
       <c r="J57" s="467" t="inlineStr">
         <is>
           <t xml:space="preserve"> SIZE   :  </t>
         </is>
       </c>
-      <c r="K57" s="548" t="inlineStr">
+      <c r="K57" s="665" t="inlineStr">
         <is>
           <t>20'</t>
         </is>
@@ -15448,7 +15458,7 @@
           <t>Description of Damage :</t>
         </is>
       </c>
-      <c r="D78" s="561" t="n"/>
+      <c r="D78" s="666" t="n"/>
       <c r="E78" s="561" t="n"/>
       <c r="F78" s="561" t="n"/>
       <c r="G78" s="561" t="n"/>
@@ -23131,7 +23141,7 @@
           <t xml:space="preserve">VOY.NO.: </t>
         </is>
       </c>
-      <c r="B6" s="345" t="n"/>
+      <c r="B6" s="137" t="n"/>
       <c r="C6" s="345">
         <f>'Final work rpt-voucher'!C6</f>
         <v/>
@@ -23147,7 +23157,7 @@
           <t>PORT  :</t>
         </is>
       </c>
-      <c r="G6" s="245" t="inlineStr">
+      <c r="G6" s="667" t="inlineStr">
         <is>
           <t>PYEONGTAEK, KOREA</t>
         </is>
@@ -24647,7 +24657,7 @@
           <t xml:space="preserve">M/V  :  </t>
         </is>
       </c>
-      <c r="B6" s="345" t="n"/>
+      <c r="B6" s="137" t="n"/>
       <c r="C6" s="345" t="n"/>
       <c r="D6" s="345" t="inlineStr">
         <is>
@@ -24677,7 +24687,7 @@
           <t>BERTH :</t>
         </is>
       </c>
-      <c r="E7" s="352" t="n">
+      <c r="E7" s="137" t="n">
         <v>15</v>
       </c>
       <c r="F7" s="636" t="n"/>
@@ -24686,7 +24696,7 @@
           <t>PORT  :</t>
         </is>
       </c>
-      <c r="H7" s="637" t="inlineStr">
+      <c r="H7" s="668" t="inlineStr">
         <is>
           <t xml:space="preserve"> PYEONGTAEK, KOREA</t>
         </is>
@@ -31463,7 +31473,7 @@
           <t xml:space="preserve">M/V  :  </t>
         </is>
       </c>
-      <c r="B53" s="345" t="n"/>
+      <c r="B53" s="137" t="n"/>
       <c r="C53" s="345" t="n"/>
       <c r="D53" s="345" t="inlineStr">
         <is>
@@ -31493,7 +31503,7 @@
           <t>BERTH :</t>
         </is>
       </c>
-      <c r="E54" s="352" t="n">
+      <c r="E54" s="137" t="n">
         <v>15</v>
       </c>
       <c r="F54" s="636" t="n"/>
@@ -31502,7 +31512,7 @@
           <t>PORT  :</t>
         </is>
       </c>
-      <c r="H54" s="637" t="inlineStr">
+      <c r="H54" s="668" t="inlineStr">
         <is>
           <t xml:space="preserve"> PYEONGTAEK, KOREA</t>
         </is>
